--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -1600,25 +1600,25 @@
         <v>26</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>50</v>
+        <v>84.62</v>
       </c>
       <c r="H31" s="1">
-        <v>50</v>
+        <v>15.38</v>
       </c>
       <c r="I31" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1">
-        <v>50</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3900,25 +3900,25 @@
         <v>26</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>50</v>
+        <v>84.62</v>
       </c>
       <c r="H31" s="1">
-        <v>50</v>
+        <v>15.38</v>
       </c>
       <c r="I31" s="2">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1">
-        <v>50</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="32" spans="1:11">

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -810,22 +810,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>12.12</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -842,22 +845,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>10.53</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -874,22 +880,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -906,22 +915,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>34.62</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -938,22 +950,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3110,22 +3125,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>12.12</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3142,22 +3160,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>10.53</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3174,22 +3195,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3206,22 +3230,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>34.62</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3238,22 +3265,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="13" spans="1:11">

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -737,19 +737,19 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>23</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>71.88</v>
+        <v>74.19</v>
       </c>
       <c r="H6" s="1">
-        <v>28.13</v>
+        <v>25.81</v>
       </c>
       <c r="I6" s="2">
         <v>7.6</v>
@@ -807,28 +807,28 @@
         <v>51</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>29</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>87.88</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>12.12</v>
+        <v>14.71</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -982,28 +982,28 @@
         <v>53</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>23</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H13" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
       <c r="I13" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K13" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1195,25 +1195,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="I19" s="2">
         <v>7.8</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1402,22 +1402,22 @@
         <v>53</v>
       </c>
       <c r="D25">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25">
         <v>41</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>97.62</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H25" s="1">
-        <v>2.38</v>
+        <v>4.65</v>
       </c>
       <c r="I25" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1542,28 +1542,28 @@
         <v>53</v>
       </c>
       <c r="D29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29">
         <v>27</v>
       </c>
       <c r="F29">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1">
-        <v>65.84999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H29" s="1">
-        <v>34.15</v>
+        <v>32.5</v>
       </c>
       <c r="I29" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29" s="1">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1807,22 +1807,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1839,22 +1842,25 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>95.12</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>4.88</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1871,22 +1877,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1903,22 +1912,25 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>92.31</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>7.69</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1932,25 +1944,28 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>19.35</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1967,22 +1982,25 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>11.36</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1996,13 +2014,13 @@
         <v>51</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -2011,7 +2029,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -2156,25 +2174,28 @@
         <v>53</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>63.33</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>36.67</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2191,22 +2212,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.5</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2287,22 +2311,25 @@
         <v>26</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>80.77</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>19.23</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2351,22 +2378,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>5.71</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2383,22 +2413,25 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2415,22 +2448,25 @@
         <v>18</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J21">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2447,22 +2483,25 @@
         <v>40</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.7</v>
       </c>
       <c r="J22">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2479,22 +2518,25 @@
         <v>44</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F23">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J23">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2511,22 +2553,25 @@
         <v>43</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F24">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>4.65</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7.8</v>
       </c>
       <c r="J24">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2540,25 +2585,28 @@
         <v>53</v>
       </c>
       <c r="D25">
+        <v>43</v>
+      </c>
+      <c r="E25">
         <v>42</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
       <c r="F25">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>97.67</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>2.33</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7.7</v>
       </c>
       <c r="J25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2668,13 +2716,13 @@
         <v>53</v>
       </c>
       <c r="D29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2683,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -2799,22 +2847,25 @@
         <v>34</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F33">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2831,22 +2882,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>15.38</v>
+      </c>
+      <c r="I34" s="2">
+        <v>7.5</v>
       </c>
       <c r="J34">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>15.38</v>
       </c>
     </row>
   </sheetData>
@@ -2915,19 +2969,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H2" s="1">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="I2" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2950,19 +3004,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>90.23999999999999</v>
+        <v>95.12</v>
       </c>
       <c r="H3" s="1">
-        <v>9.76</v>
+        <v>4.88</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2985,19 +3039,19 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3032,7 +3086,7 @@
         <v>7.69</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3052,19 +3106,19 @@
         <v>51</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>71.88</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>28.13</v>
+        <v>19.35</v>
       </c>
       <c r="I6" s="2">
         <v>7.6</v>
@@ -3090,19 +3144,19 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>81.81999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="H7" s="1">
-        <v>18.18</v>
+        <v>11.36</v>
       </c>
       <c r="I7" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3122,28 +3176,28 @@
         <v>51</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>29</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>87.88</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>12.12</v>
+        <v>14.71</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>12.12</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3297,28 +3351,28 @@
         <v>53</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>74.19</v>
+        <v>63.33</v>
       </c>
       <c r="H13" s="1">
-        <v>25.81</v>
+        <v>36.67</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K13" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3335,19 +3389,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3440,19 +3494,19 @@
         <v>26</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="H17" s="1">
-        <v>30.77</v>
+        <v>19.23</v>
       </c>
       <c r="I17" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3510,25 +3564,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="I19" s="2">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3557,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3592,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3627,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3662,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3685,19 +3739,19 @@
         <v>43</v>
       </c>
       <c r="E24">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="1">
-        <v>100</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="I24" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3717,22 +3771,22 @@
         <v>53</v>
       </c>
       <c r="D25">
+        <v>43</v>
+      </c>
+      <c r="E25">
         <v>42</v>
-      </c>
-      <c r="E25">
-        <v>41</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>97.62</v>
+        <v>97.67</v>
       </c>
       <c r="H25" s="1">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="I25" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3857,28 +3911,28 @@
         <v>53</v>
       </c>
       <c r="D29">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29">
         <v>27</v>
       </c>
       <c r="F29">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1">
-        <v>65.84999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="H29" s="1">
-        <v>34.15</v>
+        <v>32.5</v>
       </c>
       <c r="I29" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29" s="1">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4012,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4047,7 +4101,7 @@
         <v>15.38</v>
       </c>
       <c r="I34" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J34">
         <v>6</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -2017,22 +2017,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.5</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2049,22 +2052,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2081,22 +2087,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.9</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2113,22 +2122,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2145,22 +2157,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9.5</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2247,22 +2262,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2279,22 +2297,25 @@
         <v>32</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2346,22 +2367,25 @@
         <v>18</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>11.11</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2623,22 +2647,25 @@
         <v>21</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>4.76</v>
+      </c>
+      <c r="I26" s="2">
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2783,22 +2810,25 @@
         <v>26</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>38.46</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6.8</v>
       </c>
       <c r="J31">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2815,22 +2845,25 @@
         <v>15</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>46.67</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>53.33</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6.1</v>
       </c>
       <c r="J32">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3191,7 +3224,7 @@
         <v>14.71</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3249,19 +3282,19 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H10" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>2</v>
@@ -3331,7 +3364,7 @@
         <v>18.18</v>
       </c>
       <c r="I12" s="2">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -3424,19 +3457,19 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="H15" s="1">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="I15" s="2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3459,19 +3492,19 @@
         <v>32</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3529,19 +3562,19 @@
         <v>18</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H18" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I18" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3809,19 +3842,19 @@
         <v>21</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="I26" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3984,19 +4017,19 @@
         <v>26</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G31" s="1">
-        <v>84.62</v>
+        <v>61.54</v>
       </c>
       <c r="H31" s="1">
-        <v>15.38</v>
+        <v>38.46</v>
       </c>
       <c r="I31" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J31">
         <v>4</v>
@@ -4031,7 +4064,7 @@
         <v>53.33</v>
       </c>
       <c r="I32" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J32">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -2682,22 +2682,25 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F27">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>29.41</v>
+      </c>
+      <c r="I27" s="2">
+        <v>6.8</v>
       </c>
       <c r="J27">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2714,22 +2717,25 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F28">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>34.15</v>
+      </c>
+      <c r="I28" s="2">
+        <v>6.2</v>
       </c>
       <c r="J28">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2778,22 +2784,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>61.11</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>38.89</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6.4</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3877,19 +3886,19 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>76.47</v>
+        <v>70.59</v>
       </c>
       <c r="H27" s="1">
-        <v>23.53</v>
+        <v>29.41</v>
       </c>
       <c r="I27" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>4</v>
@@ -3912,16 +3921,16 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G28" s="1">
-        <v>75.61</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>24.39</v>
+        <v>34.15</v>
       </c>
       <c r="I28" s="2">
         <v>6.4</v>
@@ -3982,19 +3991,19 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1">
-        <v>75</v>
+        <v>61.11</v>
       </c>
       <c r="H30" s="1">
-        <v>25</v>
+        <v>38.89</v>
       </c>
       <c r="I30" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J30">
         <v>1</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -2752,22 +2752,25 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F29">
+        <v>16</v>
+      </c>
+      <c r="G29" s="1">
+        <v>60</v>
+      </c>
+      <c r="H29" s="1">
         <v>40</v>
       </c>
-      <c r="G29" s="1">
-        <v>0</v>
-      </c>
-      <c r="H29" s="1">
-        <v>100</v>
+      <c r="I29" s="2">
+        <v>6.2</v>
       </c>
       <c r="J29">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3956,19 +3959,19 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F29">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G29" s="1">
-        <v>67.5</v>
+        <v>60</v>
       </c>
       <c r="H29" s="1">
-        <v>32.5</v>
+        <v>40</v>
       </c>
       <c r="I29" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J29">
         <v>5</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -810,25 +810,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>14.71</v>
+        <v>11.76</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -845,25 +845,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -892,13 +892,13 @@
         <v>9.380000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -915,25 +915,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>65.38</v>
+        <v>76.92</v>
       </c>
       <c r="H11" s="1">
-        <v>34.62</v>
+        <v>23.08</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -950,25 +950,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>81.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>18.18</v>
+        <v>15.15</v>
       </c>
       <c r="I12" s="2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -997,13 +997,13 @@
         <v>23.33</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1195,25 +1195,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1475,25 +1475,25 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1">
-        <v>76.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>23.53</v>
+        <v>17.65</v>
       </c>
       <c r="I27" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1522,13 +1522,13 @@
         <v>24.39</v>
       </c>
       <c r="I28" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1545,25 +1545,25 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" s="1">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="H29" s="1">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="I29" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1595,10 +1595,10 @@
         <v>6.1</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1627,13 +1627,13 @@
         <v>15.38</v>
       </c>
       <c r="I31" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1720,25 +1720,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>15.38</v>
+        <v>10.26</v>
       </c>
       <c r="I34" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2017,25 +2017,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>50</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>50</v>
+        <v>17.65</v>
       </c>
       <c r="I8" s="2">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2052,25 +2052,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>73.68000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H9" s="1">
-        <v>26.32</v>
+        <v>13.16</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2087,25 +2087,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>81.25</v>
+        <v>93.75</v>
       </c>
       <c r="H10" s="1">
-        <v>18.75</v>
+        <v>6.25</v>
       </c>
       <c r="I10" s="2">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2122,25 +2122,25 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>50</v>
+        <v>65.38</v>
       </c>
       <c r="H11" s="1">
-        <v>50</v>
+        <v>34.62</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2157,25 +2157,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>72.73</v>
+        <v>87.88</v>
       </c>
       <c r="H12" s="1">
-        <v>27.27</v>
+        <v>12.12</v>
       </c>
       <c r="I12" s="2">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2192,25 +2192,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>36.67</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2402,25 +2402,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>9</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2682,25 +2682,25 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="H27" s="1">
-        <v>29.41</v>
+        <v>23.53</v>
       </c>
       <c r="I27" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2729,13 +2729,13 @@
         <v>34.15</v>
       </c>
       <c r="I28" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2752,25 +2752,25 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="1">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="H29" s="1">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="I29" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2799,13 +2799,13 @@
         <v>38.89</v>
       </c>
       <c r="I30" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2834,13 +2834,13 @@
         <v>38.46</v>
       </c>
       <c r="I31" s="2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2927,25 +2927,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>15.38</v>
+        <v>10.26</v>
       </c>
       <c r="I34" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3224,25 +3224,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>85.29000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>14.71</v>
+        <v>17.65</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3259,25 +3259,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>89.47</v>
+        <v>86.84</v>
       </c>
       <c r="H9" s="1">
-        <v>10.53</v>
+        <v>13.16</v>
       </c>
       <c r="I9" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3306,13 +3306,13 @@
         <v>6.25</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3341,13 +3341,13 @@
         <v>34.62</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3364,25 +3364,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H12" s="1">
-        <v>18.18</v>
+        <v>12.12</v>
       </c>
       <c r="I12" s="2">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3399,25 +3399,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>36.67</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3609,25 +3609,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3889,25 +3889,25 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>70.59</v>
+        <v>76.47</v>
       </c>
       <c r="H27" s="1">
-        <v>29.41</v>
+        <v>23.53</v>
       </c>
       <c r="I27" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3936,13 +3936,13 @@
         <v>34.15</v>
       </c>
       <c r="I28" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3959,25 +3959,25 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="1">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="H29" s="1">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="I29" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4009,10 +4009,10 @@
         <v>6.3</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4041,13 +4041,13 @@
         <v>38.46</v>
       </c>
       <c r="I31" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4134,25 +4134,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>15.38</v>
+        <v>10.26</v>
       </c>
       <c r="I34" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -3014,19 +3014,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H2" s="1">
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3049,19 +3049,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>95.12</v>
+        <v>97.56</v>
       </c>
       <c r="H3" s="1">
-        <v>4.88</v>
+        <v>2.44</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3119,19 +3119,19 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>92.31</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>7.69</v>
+        <v>10.26</v>
       </c>
       <c r="I5" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3154,19 +3154,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="H6" s="1">
-        <v>19.35</v>
+        <v>22.58</v>
       </c>
       <c r="I6" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3189,19 +3189,19 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>88.64</v>
+        <v>95.45</v>
       </c>
       <c r="H7" s="1">
-        <v>11.36</v>
+        <v>4.55</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J33">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -3236,7 +3236,7 @@
         <v>17.65</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3306,7 +3306,7 @@
         <v>6.25</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -3224,19 +3224,19 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>82.34999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>17.65</v>
+        <v>11.76</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3259,16 +3259,16 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>86.84</v>
+        <v>97.37</v>
       </c>
       <c r="H9" s="1">
-        <v>13.16</v>
+        <v>2.63</v>
       </c>
       <c r="I9" s="2">
         <v>8</v>
@@ -3329,19 +3329,19 @@
         <v>26</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>65.38</v>
+        <v>92.31</v>
       </c>
       <c r="H11" s="1">
-        <v>34.62</v>
+        <v>7.69</v>
       </c>
       <c r="I11" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3364,19 +3364,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>87.88</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>12.12</v>
+        <v>15.15</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>10.26</v>
       </c>
       <c r="I34" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J34">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3784,19 +3784,19 @@
         <v>43</v>
       </c>
       <c r="E24">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>95.34999999999999</v>
+        <v>97.67</v>
       </c>
       <c r="H24" s="1">
-        <v>4.65</v>
+        <v>2.33</v>
       </c>
       <c r="I24" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3866,7 +3866,7 @@
         <v>4.76</v>
       </c>
       <c r="I26" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3924,19 +3924,19 @@
         <v>41</v>
       </c>
       <c r="E28">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G28" s="1">
-        <v>65.84999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>34.15</v>
+        <v>7.32</v>
       </c>
       <c r="I28" s="2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3959,19 +3959,19 @@
         <v>40</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>62.5</v>
+        <v>90</v>
       </c>
       <c r="H29" s="1">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="I29" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3994,19 +3994,19 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>61.11</v>
+        <v>97.22</v>
       </c>
       <c r="H30" s="1">
-        <v>38.89</v>
+        <v>2.78</v>
       </c>
       <c r="I30" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J30">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -3889,19 +3889,19 @@
         <v>34</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>76.47</v>
+        <v>97.06</v>
       </c>
       <c r="H27" s="1">
-        <v>23.53</v>
+        <v>2.94</v>
       </c>
       <c r="I27" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -4029,19 +4029,19 @@
         <v>26</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>61.54</v>
+        <v>92.31</v>
       </c>
       <c r="H31" s="1">
-        <v>38.46</v>
+        <v>7.69</v>
       </c>
       <c r="I31" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J31">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -4064,19 +4064,19 @@
         <v>15</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>46.67</v>
+        <v>73.33</v>
       </c>
       <c r="H32" s="1">
-        <v>53.33</v>
+        <v>26.67</v>
       </c>
       <c r="I32" s="2">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="J32">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -3399,19 +3399,19 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>66.67</v>
+        <v>96.67</v>
       </c>
       <c r="H13" s="1">
-        <v>33.33</v>
+        <v>3.33</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3446,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H15" s="1">
-        <v>16.67</v>
+        <v>13.33</v>
       </c>
       <c r="I15" s="2">
         <v>7.8</v>
@@ -3504,19 +3504,19 @@
         <v>32</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3539,19 +3539,19 @@
         <v>26</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>80.77</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>19.23</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3574,19 +3574,19 @@
         <v>18</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20221.xlsx
+++ b/academias/Inglés - Estadisticos 20221.xlsx
@@ -1490,10 +1490,10 @@
         <v>6.7</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2697,10 +2697,10 @@
         <v>6.7</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3904,10 +3904,10 @@
         <v>7.3</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
